--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202606/Currency_P&L_20260623.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202606/Currency_P&L_20260623.xlsx
@@ -405,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -442,33 +442,449 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B2">
+        <v>100272798.77</v>
+      </c>
+      <c r="C2">
+        <v>-13566.45</v>
+      </c>
+      <c r="D2">
+        <v>-0.000135</v>
+      </c>
+      <c r="E2">
+        <v>126165.08</v>
+      </c>
+      <c r="F2">
+        <v>0.001257</v>
+      </c>
+      <c r="G2">
+        <v>39259.48</v>
+      </c>
+      <c r="H2">
+        <v>0.000391</v>
+      </c>
+      <c r="I2">
+        <v>-206894.56</v>
+      </c>
+      <c r="J2">
+        <v>-0.002062</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2">
+        <v>46177</v>
+      </c>
+      <c r="B3">
+        <v>98584797.62</v>
+      </c>
+      <c r="C3">
+        <v>-130406.62</v>
+      </c>
+      <c r="D3">
+        <v>-0.001301</v>
+      </c>
+      <c r="E3">
+        <v>-34501.35</v>
+      </c>
+      <c r="F3">
+        <v>-0.000344</v>
+      </c>
+      <c r="G3">
+        <v>-81604.89999999999</v>
+      </c>
+      <c r="H3">
+        <v>-0.0008140000000000001</v>
+      </c>
+      <c r="I3">
+        <v>-1328622.35</v>
+      </c>
+      <c r="J3">
+        <v>-0.01325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B4">
+        <v>92818575.01000001</v>
+      </c>
+      <c r="C4">
+        <v>-33357.75</v>
+      </c>
+      <c r="D4">
+        <v>-0.000338</v>
+      </c>
+      <c r="E4">
+        <v>-46905.5</v>
+      </c>
+      <c r="F4">
+        <v>-0.000476</v>
+      </c>
+      <c r="G4">
+        <v>-36309.27</v>
+      </c>
+      <c r="H4">
+        <v>-0.000368</v>
+      </c>
+      <c r="I4">
+        <v>-5638165.64</v>
+      </c>
+      <c r="J4">
+        <v>-0.057191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B5">
+        <v>93791423.37</v>
+      </c>
+      <c r="C5">
+        <v>-150462.36</v>
+      </c>
+      <c r="D5">
+        <v>-0.001621</v>
+      </c>
+      <c r="E5">
+        <v>-41730.13</v>
+      </c>
+      <c r="F5">
+        <v>-0.00045</v>
+      </c>
+      <c r="G5">
+        <v>-89719.28</v>
+      </c>
+      <c r="H5">
+        <v>-0.000967</v>
+      </c>
+      <c r="I5">
+        <v>1287767.41</v>
+      </c>
+      <c r="J5">
+        <v>0.013874</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B6">
+        <v>93187032.53</v>
+      </c>
+      <c r="C6">
+        <v>-53387.31</v>
+      </c>
+      <c r="D6">
+        <v>-0.000569</v>
+      </c>
+      <c r="E6">
+        <v>26028.85</v>
+      </c>
+      <c r="F6">
+        <v>0.000278</v>
+      </c>
+      <c r="G6">
+        <v>90318.94</v>
+      </c>
+      <c r="H6">
+        <v>0.000963</v>
+      </c>
+      <c r="I6">
+        <v>-686562.8</v>
+      </c>
+      <c r="J6">
+        <v>-0.00732</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B7">
+        <v>91802581.95</v>
+      </c>
+      <c r="C7">
+        <v>-38872.81</v>
+      </c>
+      <c r="D7">
+        <v>-0.000417</v>
+      </c>
+      <c r="E7">
+        <v>-20001.24</v>
+      </c>
+      <c r="F7">
+        <v>-0.000215</v>
+      </c>
+      <c r="G7">
+        <v>-34018.52</v>
+      </c>
+      <c r="H7">
+        <v>-0.000365</v>
+      </c>
+      <c r="I7">
+        <v>-1280838.24</v>
+      </c>
+      <c r="J7">
+        <v>-0.013745</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B8">
+        <v>94292397.36</v>
+      </c>
+      <c r="C8">
+        <v>-30546.56</v>
+      </c>
+      <c r="D8">
+        <v>-0.000333</v>
+      </c>
+      <c r="E8">
+        <v>-37150.86</v>
+      </c>
+      <c r="F8">
+        <v>-0.000405</v>
+      </c>
+      <c r="G8">
+        <v>33122.3</v>
+      </c>
+      <c r="H8">
+        <v>0.000361</v>
+      </c>
+      <c r="I8">
+        <v>2548986.87</v>
+      </c>
+      <c r="J8">
+        <v>0.027766</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B9">
+        <v>94675404.78</v>
+      </c>
+      <c r="C9">
+        <v>193547.22</v>
+      </c>
+      <c r="D9">
+        <v>0.002053</v>
+      </c>
+      <c r="E9">
+        <v>28272.18</v>
+      </c>
+      <c r="F9">
+        <v>0.0003</v>
+      </c>
+      <c r="G9">
+        <v>25415.54</v>
+      </c>
+      <c r="H9">
+        <v>0.00027</v>
+      </c>
+      <c r="I9">
+        <v>146244.03</v>
+      </c>
+      <c r="J9">
+        <v>0.001551</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B10">
+        <v>96432289.62</v>
+      </c>
+      <c r="C10">
+        <v>156495.61</v>
+      </c>
+      <c r="D10">
+        <v>0.001653</v>
+      </c>
+      <c r="E10">
+        <v>65983.8</v>
+      </c>
+      <c r="F10">
+        <v>0.000697</v>
+      </c>
+      <c r="G10">
+        <v>80974.99000000001</v>
+      </c>
+      <c r="H10">
+        <v>0.000855</v>
+      </c>
+      <c r="I10">
+        <v>1480049.56</v>
+      </c>
+      <c r="J10">
+        <v>0.015633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B11">
+        <v>95543307.3</v>
+      </c>
+      <c r="C11">
+        <v>7282.12</v>
+      </c>
+      <c r="D11">
+        <v>7.6E-05</v>
+      </c>
+      <c r="E11">
+        <v>-38177.24</v>
+      </c>
+      <c r="F11">
+        <v>-0.000396</v>
+      </c>
+      <c r="G11">
+        <v>92693.34</v>
+      </c>
+      <c r="H11">
+        <v>0.000961</v>
+      </c>
+      <c r="I11">
+        <v>-941747.73</v>
+      </c>
+      <c r="J11">
+        <v>-0.009766</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B12">
+        <v>95099223.72</v>
+      </c>
+      <c r="C12">
+        <v>-39972.61</v>
+      </c>
+      <c r="D12">
+        <v>-0.000418</v>
+      </c>
+      <c r="E12">
+        <v>-1829.91</v>
+      </c>
+      <c r="F12">
+        <v>-1.9E-05</v>
+      </c>
+      <c r="G12">
+        <v>53382.54</v>
+      </c>
+      <c r="H12">
+        <v>0.000559</v>
+      </c>
+      <c r="I12">
+        <v>-441419.32</v>
+      </c>
+      <c r="J12">
+        <v>-0.00462</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B13">
+        <v>95301410.52</v>
+      </c>
+      <c r="C13">
+        <v>-71085.88</v>
+      </c>
+      <c r="D13">
+        <v>-0.0007470000000000001</v>
+      </c>
+      <c r="E13">
+        <v>1046.48</v>
+      </c>
+      <c r="F13">
+        <v>1.1E-05</v>
+      </c>
+      <c r="G13">
+        <v>60361.11</v>
+      </c>
+      <c r="H13">
+        <v>0.000635</v>
+      </c>
+      <c r="I13">
+        <v>221308.09</v>
+      </c>
+      <c r="J13">
+        <v>0.002327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B14">
+        <v>95240416.18000001</v>
+      </c>
+      <c r="C14">
+        <v>36429.24</v>
+      </c>
+      <c r="D14">
+        <v>0.000382</v>
+      </c>
+      <c r="E14">
+        <v>15097.59</v>
+      </c>
+      <c r="F14">
+        <v>0.000158</v>
+      </c>
+      <c r="G14">
+        <v>31752.43</v>
+      </c>
+      <c r="H14">
+        <v>0.000333</v>
+      </c>
+      <c r="I14">
+        <v>-16714.22</v>
+      </c>
+      <c r="J14">
+        <v>-0.000175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2">
         <v>46196</v>
       </c>
-      <c r="B2">
+      <c r="B15">
         <v>93259651.5</v>
       </c>
-      <c r="C2">
+      <c r="C15">
         <v>-39051.27</v>
       </c>
-      <c r="D2">
+      <c r="D15">
         <v>-0.00041</v>
       </c>
-      <c r="E2">
+      <c r="E15">
         <v>-2621.66</v>
       </c>
-      <c r="F2">
+      <c r="F15">
         <v>-2.8E-05</v>
       </c>
-      <c r="G2">
+      <c r="G15">
         <v>23807.02</v>
       </c>
-      <c r="H2">
+      <c r="H15">
         <v>0.00025</v>
       </c>
-      <c r="I2">
+      <c r="I15">
         <v>-1961345.43</v>
       </c>
-      <c r="J2">
+      <c r="J15">
         <v>-0.020594</v>
       </c>
     </row>
